--- a/食品致病性微生物污染事件_选择题.xlsx
+++ b/食品致病性微生物污染事件_选择题.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="153">
   <si>
     <t>SN</t>
   </si>
@@ -308,6 +308,24 @@
     <t>H_11</t>
   </si>
   <si>
+    <t>采样是事故调查的重要工作内容，采样的原则有哪些?</t>
+  </si>
+  <si>
+    <t>及时性原则</t>
+  </si>
+  <si>
+    <t>针对性原则</t>
+  </si>
+  <si>
+    <t>适量性原则</t>
+  </si>
+  <si>
+    <t>不污染原则</t>
+  </si>
+  <si>
+    <t>H_12</t>
+  </si>
+  <si>
     <t>可采集的生物样本有哪些?</t>
   </si>
   <si>
@@ -323,7 +341,7 @@
     <t>呕吐物</t>
   </si>
   <si>
-    <t>H_12</t>
+    <t>H_13</t>
   </si>
   <si>
     <t>实验中检出金黄色葡萄球菌和沙门菌这两种致病菌(见上表)。基于上述资料，你认为导致这起暴发的致病因子是由什么引起的?</t>
@@ -341,130 +359,133 @@
     <t>大肠埃希氏菌</t>
   </si>
   <si>
+    <t>H_14</t>
+  </si>
+  <si>
+    <t>根据微生物检验结果，为判定同种可疑致病微生物的同源性，还需要做何检测?</t>
+  </si>
+  <si>
+    <t>荧光定量PCR</t>
+  </si>
+  <si>
+    <t>显微镜镜检法</t>
+  </si>
+  <si>
+    <t>微生物测试片检测技术</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>H_15</t>
+  </si>
+  <si>
+    <t>你认为引起食物中毒的可疑食物是什么?</t>
+  </si>
+  <si>
+    <t>素炒粉干</t>
+  </si>
+  <si>
+    <t>白灼菜心</t>
+  </si>
+  <si>
+    <t>水果拼盘</t>
+  </si>
+  <si>
+    <t>幸福煲仔</t>
+  </si>
+  <si>
+    <t>清蒸鸦片鱼</t>
+  </si>
+  <si>
+    <t>H_16</t>
+  </si>
+  <si>
+    <t>食品安全事故调查结论包括那些?</t>
+  </si>
+  <si>
+    <t>是否定性为食品安全事故</t>
+  </si>
+  <si>
+    <t>事故范围</t>
+  </si>
+  <si>
+    <t>发病人数</t>
+  </si>
+  <si>
+    <t>致病因子</t>
+  </si>
+  <si>
+    <t>污染食品及污染原因</t>
+  </si>
+  <si>
     <t>H_17</t>
   </si>
   <si>
-    <t>根据微生物检验结果，为判定同种可疑致病微生物的同源性，还需要做何检测?</t>
-  </si>
-  <si>
-    <t>荧光定量PCR</t>
-  </si>
-  <si>
-    <t>显微镜镜检法</t>
-  </si>
-  <si>
-    <t>微生物测试片检测技术</t>
-  </si>
-  <si>
-    <t>B</t>
+    <t>做出调查结论的依据包括那些?</t>
+  </si>
+  <si>
+    <t>现场流行病学调查</t>
+  </si>
+  <si>
+    <t>食品违法行为</t>
+  </si>
+  <si>
+    <t>实验室检验</t>
+  </si>
+  <si>
+    <t>是否有死亡病例</t>
+  </si>
+  <si>
+    <t>食品卫生学调查</t>
+  </si>
+  <si>
+    <t>A|C|E</t>
   </si>
   <si>
     <t>H_18</t>
   </si>
   <si>
-    <t>你认为引起食物中毒的可疑食物是什么?</t>
-  </si>
-  <si>
-    <t>素炒粉干</t>
-  </si>
-  <si>
-    <t>白灼菜心</t>
-  </si>
-  <si>
-    <t>水果拼盘</t>
-  </si>
-  <si>
-    <t>幸福煲仔</t>
-  </si>
-  <si>
-    <t>清蒸鸦片鱼</t>
+    <t>在确定致病因子、致病食品或污染原因等时，应当参照相关诊断标准或规范，并参考哪些推论原则?</t>
+  </si>
+  <si>
+    <t>现场流行病学调查结果、食品卫生学调查结果和实验室检验结果相互支持的，调查组可以做出调查结论。</t>
+  </si>
+  <si>
+    <t>现场流行病学调查结果得到食品卫生学调查或实验室检验结果之一支持的，如结果具有合理性且能够解释大部分病例的，调查组可以做出调查结论。</t>
+  </si>
+  <si>
+    <t>现场流行病学调查结果未得到食品卫生学调查和实验室检验结果支持，但现场流行病学调查结果可以判定致病因子范围、致病餐次或致病食品，经调查机构专家组3名以上具有高级职称的专家审定，可以做出调查结论。</t>
+  </si>
+  <si>
+    <t>现场流行病学调查、食品卫生学调查和实验室检验结果不能支持事故定性的，应当做出相应调查结论并说明原因。</t>
   </si>
   <si>
     <t>H_19</t>
   </si>
   <si>
-    <t>食品安全事故调查结论包括那些?</t>
-  </si>
-  <si>
-    <t>是否定性为食品安全事故</t>
-  </si>
-  <si>
-    <t>事故范围</t>
-  </si>
-  <si>
-    <t>发病人数</t>
-  </si>
-  <si>
-    <t>致病因子</t>
-  </si>
-  <si>
-    <t>污染食品及污染原因</t>
+    <t>调查结论中因果推论应当考虑哪些因素?</t>
+  </si>
+  <si>
+    <t>关联的时间顺序：可疑食品进食在前，发病在后</t>
+  </si>
+  <si>
+    <t>关联的特异性：病例均进食过可疑食品，未进食者均未发病</t>
+  </si>
+  <si>
+    <t>关联的强度：OR值或RR值越大，可疑食品与事故的因果关联性越大</t>
+  </si>
+  <si>
+    <t>剂量反应关系：进食可疑食品的数量越多，发病的危险性越高</t>
+  </si>
+  <si>
+    <t>关联的一致性:病例临床表现与检出的致病因子所致疾病的临床表现一致，或病例生物标本与可疑食品或相关的环境样品中检出的致病因子相同</t>
+  </si>
+  <si>
+    <t>终止效应:停止食用可疑食品或采取针对性的控制措施后，经过疾病的一个最长潜伏期后没有新发病例。</t>
   </si>
   <si>
     <t>H_20</t>
-  </si>
-  <si>
-    <t>做出调查结论的依据包括那些?</t>
-  </si>
-  <si>
-    <t>现场流行病学调查</t>
-  </si>
-  <si>
-    <t>食品违法行为</t>
-  </si>
-  <si>
-    <t>实验室检验</t>
-  </si>
-  <si>
-    <t>是否有死亡病例</t>
-  </si>
-  <si>
-    <t>食品卫生学调查</t>
-  </si>
-  <si>
-    <t>A|C|E</t>
-  </si>
-  <si>
-    <t>H_21</t>
-  </si>
-  <si>
-    <t>在确定致病因子、致病食品或污染原因等时，应当参照相关诊断标准或规范，并参考哪些推论原则?</t>
-  </si>
-  <si>
-    <t>现场流行病学调查结果、食品卫生学调查结果和实验室检验结果相互支持的，调查组可以做出调查结论。</t>
-  </si>
-  <si>
-    <t>现场流行病学调查结果得到食品卫生学调查或实验室检验结果之一支持的，如结果具有合理性且能够解释大部分病例的，调查组可以做出调查结论。</t>
-  </si>
-  <si>
-    <t>现场流行病学调查结果未得到食品卫生学调查和实验室检验结果支持，但现场流行病学调查结果可以判定致病因子范围、致病餐次或致病食品，经调查机构专家组3名以上具有高级职称的专家审定，可以做出调查结论。</t>
-  </si>
-  <si>
-    <t>现场流行病学调查、食品卫生学调查和实验室检验结果不能支持事故定性的，应当做出相应调查结论并说明原因。</t>
-  </si>
-  <si>
-    <t>H_22</t>
-  </si>
-  <si>
-    <t>调查结论中因果推论应当考虑哪些因素?</t>
-  </si>
-  <si>
-    <t>关联的时间顺序：可疑食品进食在前，发病在后</t>
-  </si>
-  <si>
-    <t>关联的特异性：病例均进食过可疑食品，未进食者均未发病</t>
-  </si>
-  <si>
-    <t>关联的强度：OR值或RR值越大，可疑食品与事故的因果关联性越大</t>
-  </si>
-  <si>
-    <t>剂量反应关系：进食可疑食品的数量越多，发病的危险性越高</t>
-  </si>
-  <si>
-    <t>关联的一致性:病例临床表现与检出的致病因子所致疾病的临床表现一致，或病例生物标本与可疑食品或相关的环境样品中检出的致病因子相同</t>
-  </si>
-  <si>
-    <t>终止效应:停止食用可疑食品或采取针对性的控制措施后，经过疾病的一个最长潜伏期后没有新发病例。</t>
   </si>
 </sst>
 </file>
@@ -1517,7 +1538,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N28"/>
+  <dimension ref="A1:N29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="10.1416666666667" customWidth="1"/>
@@ -1931,14 +1952,13 @@
       <c r="F12" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="G12" s="8" t="s">
+      <c r="G12" s="2" t="s">
         <v>97</v>
       </c>
       <c r="H12" s="8"/>
       <c r="J12" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="K12" s="2"/>
       <c r="L12" s="2" t="s">
         <v>23</v>
       </c>
@@ -1948,12 +1968,12 @@
         <v>98</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="2" t="s">
         <v>100</v>
       </c>
       <c r="E13" s="2" t="s">
@@ -1962,11 +1982,12 @@
       <c r="F13" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="G13" s="2" t="s">
+      <c r="G13" s="8" t="s">
         <v>103</v>
       </c>
+      <c r="H13" s="8"/>
       <c r="J13" s="2" t="s">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="K13" s="2"/>
       <c r="L13" s="2" t="s">
@@ -1983,20 +2004,20 @@
       <c r="C14" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="8" t="s">
         <v>106</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>109</v>
+        <v>40</v>
       </c>
       <c r="K14" s="2"/>
       <c r="L14" s="2" t="s">
@@ -2013,23 +2034,20 @@
       <c r="C15" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="2" t="s">
         <v>112</v>
       </c>
       <c r="E15" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F15" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="G15" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="G15" s="2" t="s">
+      <c r="J15" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="K15" s="2"/>
       <c r="L15" s="2" t="s">
@@ -2038,31 +2056,31 @@
     </row>
     <row r="16" s="2" customFormat="1" ht="55" customHeight="1" spans="1:14">
       <c r="A16" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="E16" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="G16" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="G16" s="2" t="s">
+      <c r="H16" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="H16" s="2" t="s">
-        <v>123</v>
-      </c>
       <c r="J16" s="2" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="K16" s="2"/>
       <c r="L16" s="2" t="s">
@@ -2071,31 +2089,31 @@
     </row>
     <row r="17" s="2" customFormat="1" ht="55" customHeight="1" spans="1:13">
       <c r="A17" s="7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>25</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="E17" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="G17" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="G17" s="2" t="s">
+      <c r="H17" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="H17" s="2" t="s">
-        <v>130</v>
-      </c>
       <c r="J17" s="2" t="s">
-        <v>131</v>
+        <v>32</v>
       </c>
       <c r="K17" s="2"/>
       <c r="L17" s="2" t="s">
@@ -2104,29 +2122,31 @@
     </row>
     <row r="18" s="2" customFormat="1" ht="55" customHeight="1" spans="1:13">
       <c r="A18" s="7" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>25</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="F18" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="G18" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="H18" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="G18" s="2" t="s">
+      <c r="J18" s="2" t="s">
         <v>137</v>
-      </c>
-      <c r="H18" s="2"/>
-      <c r="J18" s="2" t="s">
-        <v>71</v>
       </c>
       <c r="K18" s="2"/>
       <c r="L18" s="2" t="s">
@@ -2155,14 +2175,9 @@
       <c r="G19" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="H19" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>145</v>
-      </c>
+      <c r="H19" s="2"/>
       <c r="J19" s="2" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="K19" s="2"/>
       <c r="L19" s="2" t="s">
@@ -2170,43 +2185,72 @@
       </c>
     </row>
     <row r="20" s="2" customFormat="1" ht="55" customHeight="1" spans="1:13">
-      <c r="A20" s="7"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="8"/>
+      <c r="A20" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="21" s="2" customFormat="1" ht="55" customHeight="1" spans="1:13">
-      <c r="A21" s="7"/>
+      <c r="A21" s="7" t="s">
+        <v>152</v>
+      </c>
       <c r="B21" s="2"/>
-      <c r="C21" s="10"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="8"/>
     </row>
     <row r="22" s="2" customFormat="1" ht="55" customHeight="1" spans="1:13">
       <c r="A22" s="7"/>
       <c r="B22" s="2"/>
       <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
     </row>
     <row r="23" s="2" customFormat="1" ht="55" customHeight="1" spans="1:13">
       <c r="A23" s="7"/>
       <c r="B23" s="2"/>
       <c r="C23" s="10"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="M23" s="11"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="10"/>
     </row>
     <row r="24" s="2" customFormat="1" ht="55" customHeight="1" spans="1:13">
       <c r="A24" s="7"/>
       <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="10"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="M24" s="11"/>
     </row>
     <row r="25" s="2" customFormat="1" ht="55" customHeight="1" spans="1:13">
       <c r="A25" s="7"/>
@@ -2216,13 +2260,12 @@
       <c r="E25" s="10"/>
       <c r="F25" s="10"/>
       <c r="G25" s="10"/>
-      <c r="H25" s="10"/>
     </row>
     <row r="26" s="2" customFormat="1" ht="55" customHeight="1" spans="1:13">
       <c r="A26" s="7"/>
       <c r="B26" s="2"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="8"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="10"/>
       <c r="E26" s="10"/>
       <c r="F26" s="10"/>
       <c r="G26" s="10"/>
@@ -2231,8 +2274,8 @@
     <row r="27" s="2" customFormat="1" ht="55" customHeight="1" spans="1:13">
       <c r="A27" s="7"/>
       <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="10"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="8"/>
       <c r="E27" s="10"/>
       <c r="F27" s="10"/>
       <c r="G27" s="10"/>
@@ -2242,7 +2285,17 @@
       <c r="A28" s="7"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
-      <c r="D28" s="8"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="10"/>
+      <c r="H28" s="10"/>
+    </row>
+    <row r="29" s="2" customFormat="1" ht="55" customHeight="1" spans="1:13">
+      <c r="A29" s="7"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
